--- a/qa-docs/test-cases/API/API_VerseByVerse_Community_Test_Cases.xlsx
+++ b/qa-docs/test-cases/API/API_VerseByVerse_Community_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\versebyverse-quality-engineering\qa-docs\test-cases\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7017B37B-0F5D-463D-B824-2E0E10660DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0E7154-595D-4A3C-B8A7-D498934E3B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
